--- a/artfynd/A 30863-2025 artfynd.xlsx
+++ b/artfynd/A 30863-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126410835</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126411785</v>
       </c>
       <c r="B3" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126411449</v>
       </c>
       <c r="B4" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30863-2025 artfynd.xlsx
+++ b/artfynd/A 30863-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>126696925</v>
       </c>
       <c r="B5" t="n">
-        <v>95857</v>
+        <v>95932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126696891</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30863-2025 artfynd.xlsx
+++ b/artfynd/A 30863-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>126696925</v>
       </c>
       <c r="B5" t="n">
-        <v>95932</v>
+        <v>95938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126696891</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30863-2025 artfynd.xlsx
+++ b/artfynd/A 30863-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>126696925</v>
       </c>
       <c r="B5" t="n">
-        <v>95938</v>
+        <v>95939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30863-2025 artfynd.xlsx
+++ b/artfynd/A 30863-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>126696925</v>
       </c>
       <c r="B5" t="n">
-        <v>95939</v>
+        <v>95932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126696891</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
